--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseLine" sheetId="1" r:id="rId1"/>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="205">
   <si>
     <t>id</t>
   </si>
@@ -948,7 +948,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -977,6 +977,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1494,16 +1500,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1512,119 +1515,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1671,6 +1677,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2558,7 +2567,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z425"/>
+  <dimension ref="A1:Z430"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -13107,6 +13116,121 @@
         <v>5</v>
       </c>
       <c r="G425" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" customFormat="1" spans="1:7">
+      <c r="A426" s="16">
+        <v>60550001</v>
+      </c>
+      <c r="B426" s="6">
+        <v>105500</v>
+      </c>
+      <c r="C426" s="7">
+        <v>1</v>
+      </c>
+      <c r="D426" s="16">
+        <v>1</v>
+      </c>
+      <c r="E426" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F426" s="7">
+        <v>5</v>
+      </c>
+      <c r="G426" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" customFormat="1" spans="1:7">
+      <c r="A427" s="16">
+        <v>60550002</v>
+      </c>
+      <c r="B427" s="6">
+        <v>105500</v>
+      </c>
+      <c r="C427" s="7">
+        <v>2</v>
+      </c>
+      <c r="D427" s="16">
+        <v>1</v>
+      </c>
+      <c r="E427" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F427" s="7">
+        <v>5</v>
+      </c>
+      <c r="G427" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" customFormat="1" spans="1:7">
+      <c r="A428" s="16">
+        <v>60550003</v>
+      </c>
+      <c r="B428" s="6">
+        <v>105500</v>
+      </c>
+      <c r="C428" s="7">
+        <v>3</v>
+      </c>
+      <c r="D428" s="16">
+        <v>1</v>
+      </c>
+      <c r="E428" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F428" s="7">
+        <v>5</v>
+      </c>
+      <c r="G428" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" customFormat="1" spans="1:7">
+      <c r="A429" s="16">
+        <v>60550004</v>
+      </c>
+      <c r="B429" s="6">
+        <v>105500</v>
+      </c>
+      <c r="C429" s="7">
+        <v>4</v>
+      </c>
+      <c r="D429" s="16">
+        <v>1</v>
+      </c>
+      <c r="E429" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F429" s="7">
+        <v>5</v>
+      </c>
+      <c r="G429" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" customFormat="1" spans="1:7">
+      <c r="A430" s="16">
+        <v>60550005</v>
+      </c>
+      <c r="B430" s="6">
+        <v>105500</v>
+      </c>
+      <c r="C430" s="7">
+        <v>5</v>
+      </c>
+      <c r="D430" s="16">
+        <v>1</v>
+      </c>
+      <c r="E430" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F430" s="7">
+        <v>5</v>
+      </c>
+      <c r="G430" s="16">
         <v>0</v>
       </c>
     </row>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="205">
   <si>
     <t>id</t>
   </si>
@@ -2567,7 +2567,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z430"/>
+  <dimension ref="A1:Z435"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
@@ -13231,6 +13231,121 @@
         <v>5</v>
       </c>
       <c r="G430" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" customFormat="1" spans="1:7">
+      <c r="A431" s="16">
+        <v>60550101</v>
+      </c>
+      <c r="B431" s="6">
+        <v>105501</v>
+      </c>
+      <c r="C431" s="7">
+        <v>1</v>
+      </c>
+      <c r="D431" s="16">
+        <v>1</v>
+      </c>
+      <c r="E431" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="F431" s="7">
+        <v>5</v>
+      </c>
+      <c r="G431" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" customFormat="1" spans="1:7">
+      <c r="A432" s="16">
+        <v>60550102</v>
+      </c>
+      <c r="B432" s="6">
+        <v>105501</v>
+      </c>
+      <c r="C432" s="7">
+        <v>2</v>
+      </c>
+      <c r="D432" s="16">
+        <v>1</v>
+      </c>
+      <c r="E432" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F432" s="7">
+        <v>5</v>
+      </c>
+      <c r="G432" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" customFormat="1" spans="1:7">
+      <c r="A433" s="16">
+        <v>60550103</v>
+      </c>
+      <c r="B433" s="6">
+        <v>105501</v>
+      </c>
+      <c r="C433" s="7">
+        <v>3</v>
+      </c>
+      <c r="D433" s="16">
+        <v>1</v>
+      </c>
+      <c r="E433" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F433" s="7">
+        <v>5</v>
+      </c>
+      <c r="G433" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" customFormat="1" spans="1:7">
+      <c r="A434" s="16">
+        <v>60550104</v>
+      </c>
+      <c r="B434" s="6">
+        <v>105501</v>
+      </c>
+      <c r="C434" s="7">
+        <v>4</v>
+      </c>
+      <c r="D434" s="16">
+        <v>1</v>
+      </c>
+      <c r="E434" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F434" s="7">
+        <v>5</v>
+      </c>
+      <c r="G434" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" customFormat="1" spans="1:7">
+      <c r="A435" s="16">
+        <v>60550105</v>
+      </c>
+      <c r="B435" s="6">
+        <v>105501</v>
+      </c>
+      <c r="C435" s="7">
+        <v>5</v>
+      </c>
+      <c r="D435" s="16">
+        <v>1</v>
+      </c>
+      <c r="E435" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F435" s="7">
+        <v>5</v>
+      </c>
+      <c r="G435" s="16">
         <v>0</v>
       </c>
     </row>

--- a/slots/resources/sample/BaseLine.xlsx
+++ b/slots/resources/sample/BaseLine.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB604D43-F78F-46D8-849C-88E7E3CA32D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseLine" sheetId="1" r:id="rId1"/>
@@ -31,13 +37,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author/>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -51,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="1">
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -75,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -94,7 +100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -111,13 +117,13 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author/>
   </authors>
   <commentList>
-    <comment ref="G20" authorId="0">
+    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -130,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J20" authorId="1">
+    <comment ref="J20" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -173,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K20" authorId="1">
+    <comment ref="K20" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -197,7 +203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M20" authorId="1">
+    <comment ref="M20" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -221,7 +227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N20" authorId="1">
+    <comment ref="N20" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -243,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="1">
+    <comment ref="P20" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -265,7 +271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q20" authorId="0">
+    <comment ref="Q20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -284,7 +290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R20" authorId="1">
+    <comment ref="R20" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -321,7 +327,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="205">
   <si>
     <t>id</t>
   </si>
@@ -941,14 +947,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -986,150 +986,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1140,8 +996,35 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1162,204 +1045,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1382,255 +1079,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1682,59 +1137,184 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1748,12 +1328,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -1767,9 +1350,15 @@
       <xdr:row>45</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="10" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1802,9 +1391,15 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9505567" cy="9816255"/>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="11" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1842,9 +1437,15 @@
       <xdr:row>51</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="12" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1877,9 +1478,15 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9505567" cy="9816255"/>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="13" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1917,9 +1524,15 @@
       <xdr:row>51</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="14" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1952,9 +1565,15 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9505567" cy="9816255"/>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="15" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1992,9 +1611,15 @@
       <xdr:row>51</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="16" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2027,9 +1652,15 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9505567" cy="9816255"/>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="17" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2062,9 +1693,15 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9505567" cy="9816255"/>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="2" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2102,9 +1739,15 @@
       <xdr:row>132</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="3" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2137,9 +1780,15 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9505567" cy="9816255"/>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="4" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2177,9 +1826,15 @@
       <xdr:row>132</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="5" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2212,9 +1867,15 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9505567" cy="9816255"/>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="6" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2252,9 +1913,15 @@
       <xdr:row>132</xdr:row>
       <xdr:rowOff>176530</xdr:rowOff>
     </xdr:to>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="7" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2287,9 +1954,15 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9505567" cy="9816255"/>
-    <xdr:sp>
+    <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="CustomShape 1" hidden="1"/>
+        <xdr:cNvPr id="8" name="CustomShape 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2561,14 +2234,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:Z435"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z440"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.375"/>
     <col min="2" max="2" width="11.375" style="6" customWidth="1"/>
@@ -2576,11 +2249,11 @@
     <col min="4" max="4" width="14.5" style="9" customWidth="1"/>
     <col min="5" max="5" width="16.375" style="7" customWidth="1"/>
     <col min="6" max="6" width="12.25" style="7" customWidth="1"/>
-    <col min="7" max="7" width="12.9416666666667" style="9" customWidth="1"/>
+    <col min="7" max="7" width="13" style="9" customWidth="1"/>
     <col min="8" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="33" customHeight="1" spans="1:26">
+    <row r="1" spans="1:26" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2603,7 +2276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="5" customFormat="1" spans="1:26">
+    <row r="2" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
@@ -2626,7 +2299,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="5" customFormat="1" spans="1:26">
+    <row r="3" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2649,13 +2322,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" s="5" customFormat="1" spans="1:26">
+    <row r="4" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" s="5" customFormat="1" spans="1:26">
+    <row r="5" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="5">
         <f t="shared" ref="A5:A36" si="0">(B5+500000)*100+C5+G5*1000</f>
         <v>60010001</v>
@@ -2679,7 +2352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>60010002</v>
@@ -2703,7 +2376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A7" s="5">
         <f t="shared" si="0"/>
         <v>60010003</v>
@@ -2727,7 +2400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A8" s="5">
         <f t="shared" si="0"/>
         <v>60010004</v>
@@ -2751,7 +2424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A9" s="5">
         <f t="shared" si="0"/>
         <v>60010005</v>
@@ -2775,7 +2448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A10" s="5">
         <f t="shared" si="0"/>
         <v>60010006</v>
@@ -2799,7 +2472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A11" s="5">
         <f t="shared" si="0"/>
         <v>60010007</v>
@@ -2823,7 +2496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A12" s="5">
         <f t="shared" si="0"/>
         <v>60010008</v>
@@ -2847,7 +2520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A13" s="5">
         <f t="shared" si="0"/>
         <v>60010009</v>
@@ -2871,7 +2544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A14" s="5">
         <f t="shared" si="0"/>
         <v>60010010</v>
@@ -2895,7 +2568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A15" s="5">
         <f t="shared" si="0"/>
         <v>60010011</v>
@@ -2919,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A16" s="5">
         <f t="shared" si="0"/>
         <v>60010012</v>
@@ -2958,7 +2631,7 @@
       <c r="Y16"/>
       <c r="Z16"/>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A17" s="5">
         <f t="shared" si="0"/>
         <v>60010013</v>
@@ -2997,7 +2670,7 @@
       <c r="Y17"/>
       <c r="Z17"/>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>60010014</v>
@@ -3036,7 +2709,7 @@
       <c r="Y18"/>
       <c r="Z18"/>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A19" s="5">
         <f t="shared" si="0"/>
         <v>60010015</v>
@@ -3075,7 +2748,7 @@
       <c r="Y19"/>
       <c r="Z19"/>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A20" s="5">
         <f t="shared" si="0"/>
         <v>60010016</v>
@@ -3114,7 +2787,7 @@
       <c r="Y20"/>
       <c r="Z20"/>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A21" s="5">
         <f t="shared" si="0"/>
         <v>60010017</v>
@@ -3153,7 +2826,7 @@
       <c r="Y21"/>
       <c r="Z21"/>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A22" s="5">
         <f t="shared" si="0"/>
         <v>60010018</v>
@@ -3192,7 +2865,7 @@
       <c r="Y22"/>
       <c r="Z22"/>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A23" s="5">
         <f t="shared" si="0"/>
         <v>60010019</v>
@@ -3231,7 +2904,7 @@
       <c r="Y23"/>
       <c r="Z23"/>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A24" s="5">
         <f t="shared" si="0"/>
         <v>60010020</v>
@@ -3270,7 +2943,7 @@
       <c r="Y24"/>
       <c r="Z24"/>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A25" s="5">
         <f t="shared" si="0"/>
         <v>60010021</v>
@@ -3294,7 +2967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A26" s="5">
         <f t="shared" si="0"/>
         <v>60010022</v>
@@ -3318,7 +2991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:26">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A27" s="5">
         <f t="shared" si="0"/>
         <v>60010023</v>
@@ -3342,7 +3015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:26">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A28" s="5">
         <f t="shared" si="0"/>
         <v>60010024</v>
@@ -3366,7 +3039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:26">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A29" s="5">
         <f t="shared" si="0"/>
         <v>60010025</v>
@@ -3390,7 +3063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:26">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A30" s="5">
         <f t="shared" si="0"/>
         <v>60010026</v>
@@ -3414,7 +3087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:26">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A31" s="5">
         <f t="shared" si="0"/>
         <v>60010027</v>
@@ -3438,7 +3111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:26">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A32" s="5">
         <f t="shared" si="0"/>
         <v>60010028</v>
@@ -3462,7 +3135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="5">
         <f t="shared" si="0"/>
         <v>60010029</v>
@@ -3486,7 +3159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="5">
         <f t="shared" si="0"/>
         <v>60010030</v>
@@ -3510,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="5">
         <f t="shared" si="0"/>
         <v>60010031</v>
@@ -3534,7 +3207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="5">
         <f t="shared" si="0"/>
         <v>60010032</v>
@@ -3558,7 +3231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="5">
         <f t="shared" ref="A37:A68" si="1">(B37+500000)*100+C37+G37*1000</f>
         <v>60010033</v>
@@ -3582,7 +3255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="5">
         <f t="shared" si="1"/>
         <v>60010034</v>
@@ -3606,7 +3279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="5">
         <f t="shared" si="1"/>
         <v>60010035</v>
@@ -3630,7 +3303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="5">
         <f t="shared" si="1"/>
         <v>60010036</v>
@@ -3654,7 +3327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="5">
         <f t="shared" si="1"/>
         <v>60010037</v>
@@ -3678,7 +3351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="5">
         <f t="shared" si="1"/>
         <v>60010038</v>
@@ -3702,7 +3375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="5">
         <f t="shared" si="1"/>
         <v>60010039</v>
@@ -3726,7 +3399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="5">
         <f t="shared" si="1"/>
         <v>60010040</v>
@@ -3750,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="5">
         <f t="shared" si="1"/>
         <v>60010041</v>
@@ -3774,7 +3447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="5">
         <f t="shared" si="1"/>
         <v>60010042</v>
@@ -3798,7 +3471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="5">
         <f t="shared" si="1"/>
         <v>60010043</v>
@@ -3822,7 +3495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="5">
         <f t="shared" si="1"/>
         <v>60010044</v>
@@ -3846,7 +3519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A49" s="5">
         <f t="shared" si="1"/>
         <v>60010045</v>
@@ -3870,7 +3543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="5">
         <f t="shared" si="1"/>
         <v>60010046</v>
@@ -3894,7 +3567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="5">
         <f t="shared" si="1"/>
         <v>60010047</v>
@@ -3918,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="5">
         <f t="shared" si="1"/>
         <v>60010048</v>
@@ -3942,7 +3615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="5">
         <f t="shared" si="1"/>
         <v>60010049</v>
@@ -3966,7 +3639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="5">
         <f t="shared" si="1"/>
         <v>60010050</v>
@@ -3990,7 +3663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="5">
         <f t="shared" si="1"/>
         <v>60030001</v>
@@ -4014,7 +3687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="5">
         <f t="shared" si="1"/>
         <v>60120001</v>
@@ -4041,7 +3714,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A57" s="5">
         <f t="shared" si="1"/>
         <v>60120002</v>
@@ -4068,7 +3741,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A58" s="5">
         <f t="shared" si="1"/>
         <v>60120003</v>
@@ -4095,7 +3768,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A59" s="5">
         <f t="shared" si="1"/>
         <v>60120004</v>
@@ -4122,7 +3795,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="5">
         <f t="shared" si="1"/>
         <v>60120005</v>
@@ -4149,7 +3822,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="5">
         <f t="shared" si="1"/>
         <v>60120006</v>
@@ -4176,7 +3849,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="5">
         <f t="shared" si="1"/>
         <v>60120007</v>
@@ -4203,7 +3876,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="5">
         <f t="shared" si="1"/>
         <v>60120008</v>
@@ -4230,7 +3903,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="5">
         <f t="shared" si="1"/>
         <v>60120009</v>
@@ -4257,7 +3930,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="5">
         <f t="shared" si="1"/>
         <v>60120010</v>
@@ -4284,7 +3957,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="5">
         <f t="shared" si="1"/>
         <v>60120011</v>
@@ -4311,7 +3984,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="5">
         <f t="shared" si="1"/>
         <v>60120012</v>
@@ -4338,7 +4011,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="5">
         <f t="shared" si="1"/>
         <v>60120013</v>
@@ -4365,7 +4038,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="5">
         <f t="shared" ref="A69:A86" si="2">(B69+500000)*100+C69+G69*1000</f>
         <v>60120014</v>
@@ -4392,7 +4065,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="5">
         <f t="shared" si="2"/>
         <v>60120015</v>
@@ -4419,7 +4092,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="5">
         <f t="shared" si="2"/>
         <v>60120016</v>
@@ -4446,7 +4119,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A72" s="5">
         <f t="shared" si="2"/>
         <v>60120017</v>
@@ -4473,7 +4146,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A73" s="5">
         <f t="shared" si="2"/>
         <v>60120018</v>
@@ -4500,7 +4173,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A74" s="5">
         <f t="shared" si="2"/>
         <v>60120019</v>
@@ -4527,7 +4200,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A75" s="5">
         <f t="shared" si="2"/>
         <v>60120020</v>
@@ -4554,7 +4227,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A76" s="5">
         <f t="shared" si="2"/>
         <v>60120021</v>
@@ -4581,7 +4254,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A77" s="5">
         <f t="shared" si="2"/>
         <v>60120022</v>
@@ -4608,7 +4281,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A78" s="5">
         <f t="shared" si="2"/>
         <v>60120023</v>
@@ -4635,7 +4308,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A79" s="5">
         <f t="shared" si="2"/>
         <v>60120024</v>
@@ -4662,7 +4335,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A80" s="5">
         <f t="shared" si="2"/>
         <v>60120025</v>
@@ -4689,7 +4362,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A81" s="5">
         <f t="shared" si="2"/>
         <v>60120026</v>
@@ -4716,7 +4389,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A82" s="5">
         <f t="shared" si="2"/>
         <v>60120027</v>
@@ -4743,7 +4416,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A83" s="5">
         <f t="shared" si="2"/>
         <v>60120028</v>
@@ -4770,7 +4443,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A84" s="5">
         <f t="shared" si="2"/>
         <v>60120029</v>
@@ -4797,7 +4470,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A85" s="5">
         <f t="shared" si="2"/>
         <v>60120030</v>
@@ -4824,7 +4497,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86" s="5" customFormat="1" spans="1:8">
+    <row r="86" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A86" s="5">
         <f t="shared" si="2"/>
         <v>60240001</v>
@@ -4848,7 +4521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A87" s="5">
         <f t="shared" ref="A87:A118" si="3">(B87+500000)*100+C87+G87*1000</f>
         <v>60240002</v>
@@ -4872,7 +4545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A88" s="5">
         <f t="shared" si="3"/>
         <v>60240003</v>
@@ -4896,7 +4569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A89" s="5">
         <f t="shared" si="3"/>
         <v>60240004</v>
@@ -4920,7 +4593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A90" s="5">
         <f t="shared" si="3"/>
         <v>60240005</v>
@@ -4944,7 +4617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A91" s="5">
         <f t="shared" si="3"/>
         <v>60240006</v>
@@ -4968,7 +4641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A92" s="5">
         <f t="shared" si="3"/>
         <v>60240007</v>
@@ -4992,7 +4665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A93" s="5">
         <f t="shared" si="3"/>
         <v>60240008</v>
@@ -5016,7 +4689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A94" s="5">
         <f t="shared" si="3"/>
         <v>60240009</v>
@@ -5040,7 +4713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A95" s="5">
         <f t="shared" si="3"/>
         <v>60240010</v>
@@ -5064,7 +4737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A96" s="5">
         <f t="shared" si="3"/>
         <v>60240011</v>
@@ -5088,7 +4761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:26">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A97" s="5">
         <f t="shared" si="3"/>
         <v>60240012</v>
@@ -5127,7 +4800,7 @@
       <c r="Y97"/>
       <c r="Z97"/>
     </row>
-    <row r="98" spans="1:26">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A98" s="5">
         <f t="shared" si="3"/>
         <v>60240013</v>
@@ -5166,7 +4839,7 @@
       <c r="Y98"/>
       <c r="Z98"/>
     </row>
-    <row r="99" spans="1:26">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A99" s="5">
         <f t="shared" si="3"/>
         <v>60240014</v>
@@ -5205,7 +4878,7 @@
       <c r="Y99"/>
       <c r="Z99"/>
     </row>
-    <row r="100" spans="1:26">
+    <row r="100" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A100" s="5">
         <f t="shared" si="3"/>
         <v>60240015</v>
@@ -5244,7 +4917,7 @@
       <c r="Y100"/>
       <c r="Z100"/>
     </row>
-    <row r="101" spans="1:26">
+    <row r="101" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A101" s="5">
         <f t="shared" si="3"/>
         <v>60240016</v>
@@ -5283,7 +4956,7 @@
       <c r="Y101"/>
       <c r="Z101"/>
     </row>
-    <row r="102" spans="1:26">
+    <row r="102" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A102" s="5">
         <f t="shared" si="3"/>
         <v>60240017</v>
@@ -5322,7 +4995,7 @@
       <c r="Y102"/>
       <c r="Z102"/>
     </row>
-    <row r="103" spans="1:26">
+    <row r="103" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A103" s="5">
         <f t="shared" si="3"/>
         <v>60240018</v>
@@ -5361,7 +5034,7 @@
       <c r="Y103"/>
       <c r="Z103"/>
     </row>
-    <row r="104" spans="1:26">
+    <row r="104" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A104" s="5">
         <f t="shared" si="3"/>
         <v>60240019</v>
@@ -5400,7 +5073,7 @@
       <c r="Y104"/>
       <c r="Z104"/>
     </row>
-    <row r="105" spans="1:26">
+    <row r="105" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A105" s="5">
         <f t="shared" si="3"/>
         <v>60240020</v>
@@ -5439,7 +5112,7 @@
       <c r="Y105"/>
       <c r="Z105"/>
     </row>
-    <row r="106" spans="1:26">
+    <row r="106" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A106" s="5">
         <f t="shared" si="3"/>
         <v>60240021</v>
@@ -5463,7 +5136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:26">
+    <row r="107" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A107" s="5">
         <f t="shared" si="3"/>
         <v>60240022</v>
@@ -5487,7 +5160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:26">
+    <row r="108" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A108" s="5">
         <f t="shared" si="3"/>
         <v>60240023</v>
@@ -5511,7 +5184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:26">
+    <row r="109" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A109" s="5">
         <f t="shared" si="3"/>
         <v>60240024</v>
@@ -5535,7 +5208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:26">
+    <row r="110" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A110" s="5">
         <f t="shared" si="3"/>
         <v>60240025</v>
@@ -5559,7 +5232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:26">
+    <row r="111" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A111" s="5">
         <f t="shared" si="3"/>
         <v>60240026</v>
@@ -5583,7 +5256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:26">
+    <row r="112" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A112" s="5">
         <f t="shared" si="3"/>
         <v>60240027</v>
@@ -5607,7 +5280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A113" s="5">
         <f t="shared" si="3"/>
         <v>60240028</v>
@@ -5631,7 +5304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A114" s="5">
         <f t="shared" si="3"/>
         <v>60240029</v>
@@ -5655,7 +5328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A115" s="5">
         <f t="shared" si="3"/>
         <v>60240030</v>
@@ -5679,7 +5352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A116" s="5">
         <f t="shared" si="3"/>
         <v>60240031</v>
@@ -5703,7 +5376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A117" s="5">
         <f t="shared" si="3"/>
         <v>60240032</v>
@@ -5727,7 +5400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A118" s="5">
         <f t="shared" si="3"/>
         <v>60240033</v>
@@ -5751,7 +5424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A119" s="5">
         <f t="shared" ref="A119:A150" si="4">(B119+500000)*100+C119+G119*1000</f>
         <v>60240034</v>
@@ -5775,7 +5448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A120" s="5">
         <f t="shared" si="4"/>
         <v>60240035</v>
@@ -5799,7 +5472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A121" s="5">
         <f t="shared" si="4"/>
         <v>60240036</v>
@@ -5823,7 +5496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A122" s="5">
         <f t="shared" si="4"/>
         <v>60240037</v>
@@ -5847,7 +5520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A123" s="5">
         <f t="shared" si="4"/>
         <v>60240038</v>
@@ -5871,7 +5544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A124" s="5">
         <f t="shared" si="4"/>
         <v>60240039</v>
@@ -5895,7 +5568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A125" s="5">
         <f t="shared" si="4"/>
         <v>60240040</v>
@@ -5919,7 +5592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A126" s="5">
         <f t="shared" si="4"/>
         <v>60240041</v>
@@ -5943,7 +5616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A127" s="5">
         <f t="shared" si="4"/>
         <v>60240042</v>
@@ -5967,7 +5640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A128" s="5">
         <f t="shared" si="4"/>
         <v>60240043</v>
@@ -5991,7 +5664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A129" s="5">
         <f t="shared" si="4"/>
         <v>60240044</v>
@@ -6015,7 +5688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A130" s="5">
         <f t="shared" si="4"/>
         <v>60240045</v>
@@ -6039,7 +5712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A131" s="5">
         <f t="shared" si="4"/>
         <v>60240046</v>
@@ -6063,7 +5736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A132" s="5">
         <f t="shared" si="4"/>
         <v>60240047</v>
@@ -6087,7 +5760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A133" s="5">
         <f t="shared" si="4"/>
         <v>60240048</v>
@@ -6111,7 +5784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A134" s="5">
         <f t="shared" si="4"/>
         <v>60240049</v>
@@ -6135,7 +5808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A135" s="5">
         <f t="shared" si="4"/>
         <v>60240050</v>
@@ -6159,7 +5832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A136" s="5">
         <f t="shared" si="4"/>
         <v>60221001</v>
@@ -6183,7 +5856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A137" s="5">
         <f t="shared" si="4"/>
         <v>60221002</v>
@@ -6207,7 +5880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A138" s="5">
         <f t="shared" si="4"/>
         <v>60221003</v>
@@ -6231,7 +5904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A139" s="5">
         <f t="shared" si="4"/>
         <v>60221004</v>
@@ -6255,7 +5928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A140" s="5">
         <f t="shared" si="4"/>
         <v>60221005</v>
@@ -6279,7 +5952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A141" s="5">
         <f t="shared" si="4"/>
         <v>60221006</v>
@@ -6303,7 +5976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A142" s="5">
         <f t="shared" si="4"/>
         <v>60221007</v>
@@ -6327,7 +6000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A143" s="5">
         <f t="shared" si="4"/>
         <v>60221008</v>
@@ -6351,7 +6024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A144" s="5">
         <f t="shared" si="4"/>
         <v>60221009</v>
@@ -6375,7 +6048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A145" s="5">
         <f t="shared" si="4"/>
         <v>60221010</v>
@@ -6399,7 +6072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A146" s="5">
         <f t="shared" si="4"/>
         <v>60221011</v>
@@ -6423,7 +6096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A147" s="5">
         <f t="shared" si="4"/>
         <v>60221012</v>
@@ -6447,7 +6120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A148" s="5">
         <f t="shared" si="4"/>
         <v>60221013</v>
@@ -6471,7 +6144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A149" s="5">
         <f t="shared" si="4"/>
         <v>60221014</v>
@@ -6495,7 +6168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A150" s="5">
         <f t="shared" si="4"/>
         <v>60221015</v>
@@ -6519,7 +6192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A151" s="5">
         <f t="shared" ref="A151:A185" si="5">(B151+500000)*100+C151+G151*1000</f>
         <v>60221016</v>
@@ -6543,7 +6216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A152" s="5">
         <f t="shared" si="5"/>
         <v>60221017</v>
@@ -6567,7 +6240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A153" s="5">
         <f t="shared" si="5"/>
         <v>60221018</v>
@@ -6591,7 +6264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A154" s="5">
         <f t="shared" si="5"/>
         <v>60221019</v>
@@ -6615,7 +6288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A155" s="5">
         <f t="shared" si="5"/>
         <v>60221020</v>
@@ -6639,7 +6312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A156" s="5">
         <f t="shared" si="5"/>
         <v>60221021</v>
@@ -6663,7 +6336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A157" s="5">
         <f t="shared" si="5"/>
         <v>60221022</v>
@@ -6687,7 +6360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A158" s="5">
         <f t="shared" si="5"/>
         <v>60221023</v>
@@ -6711,7 +6384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A159" s="5">
         <f t="shared" si="5"/>
         <v>60221024</v>
@@ -6735,7 +6408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A160" s="5">
         <f t="shared" si="5"/>
         <v>60221025</v>
@@ -6759,7 +6432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A161" s="5">
         <f t="shared" si="5"/>
         <v>60222001</v>
@@ -6783,7 +6456,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A162" s="5">
         <f t="shared" si="5"/>
         <v>60222002</v>
@@ -6807,7 +6480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A163" s="5">
         <f t="shared" si="5"/>
         <v>60222003</v>
@@ -6831,7 +6504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A164" s="5">
         <f t="shared" si="5"/>
         <v>60222004</v>
@@ -6855,7 +6528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A165" s="5">
         <f t="shared" si="5"/>
         <v>60222005</v>
@@ -6879,7 +6552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A166" s="5">
         <f t="shared" si="5"/>
         <v>60222006</v>
@@ -6903,7 +6576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A167" s="5">
         <f t="shared" si="5"/>
         <v>60222007</v>
@@ -6927,7 +6600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A168" s="5">
         <f t="shared" si="5"/>
         <v>60222008</v>
@@ -6951,7 +6624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A169" s="5">
         <f t="shared" si="5"/>
         <v>60222009</v>
@@ -6975,7 +6648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A170" s="5">
         <f t="shared" si="5"/>
         <v>60222010</v>
@@ -6999,7 +6672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A171" s="5">
         <f t="shared" si="5"/>
         <v>60222011</v>
@@ -7023,7 +6696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A172" s="5">
         <f t="shared" si="5"/>
         <v>60222012</v>
@@ -7047,7 +6720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A173" s="5">
         <f t="shared" si="5"/>
         <v>60222013</v>
@@ -7071,7 +6744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A174" s="5">
         <f t="shared" si="5"/>
         <v>60222014</v>
@@ -7095,7 +6768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A175" s="5">
         <f t="shared" si="5"/>
         <v>60222015</v>
@@ -7119,7 +6792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A176" s="5">
         <f t="shared" si="5"/>
         <v>60222016</v>
@@ -7143,7 +6816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A177" s="5">
         <f t="shared" si="5"/>
         <v>60222017</v>
@@ -7167,7 +6840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A178" s="5">
         <f t="shared" si="5"/>
         <v>60222018</v>
@@ -7191,7 +6864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A179" s="5">
         <f t="shared" si="5"/>
         <v>60222019</v>
@@ -7215,7 +6888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A180" s="5">
         <f t="shared" si="5"/>
         <v>60222020</v>
@@ -7239,7 +6912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A181" s="5">
         <f t="shared" si="5"/>
         <v>60222021</v>
@@ -7263,7 +6936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A182" s="5">
         <f t="shared" si="5"/>
         <v>60222022</v>
@@ -7287,7 +6960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A183" s="5">
         <f t="shared" si="5"/>
         <v>60222023</v>
@@ -7311,7 +6984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A184" s="5">
         <f t="shared" si="5"/>
         <v>60222024</v>
@@ -7335,7 +7008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A185" s="5">
         <f t="shared" si="5"/>
         <v>60222025</v>
@@ -7359,7 +7032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A186" s="5">
         <f t="shared" ref="A186:A217" si="6">(B186+500000)*100+C186+G186*1000</f>
         <v>60250001</v>
@@ -7383,7 +7056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A187" s="5">
         <f t="shared" si="6"/>
         <v>60250002</v>
@@ -7407,7 +7080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A188" s="5">
         <f t="shared" si="6"/>
         <v>60250003</v>
@@ -7431,7 +7104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A189" s="5">
         <f t="shared" si="6"/>
         <v>60250004</v>
@@ -7455,7 +7128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A190" s="5">
         <f t="shared" si="6"/>
         <v>60250005</v>
@@ -7479,7 +7152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A191" s="5">
         <f t="shared" si="6"/>
         <v>60250006</v>
@@ -7503,7 +7176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A192" s="5">
         <f t="shared" si="6"/>
         <v>60250007</v>
@@ -7527,7 +7200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A193" s="5">
         <f t="shared" si="6"/>
         <v>60250008</v>
@@ -7551,7 +7224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A194" s="5">
         <f t="shared" si="6"/>
         <v>60250009</v>
@@ -7575,7 +7248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A195" s="5">
         <f t="shared" si="6"/>
         <v>60250010</v>
@@ -7599,7 +7272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A196" s="5">
         <f t="shared" si="6"/>
         <v>60250011</v>
@@ -7623,7 +7296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A197" s="5">
         <f t="shared" si="6"/>
         <v>60250012</v>
@@ -7647,7 +7320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A198" s="5">
         <f t="shared" si="6"/>
         <v>60250013</v>
@@ -7671,7 +7344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A199" s="5">
         <f t="shared" si="6"/>
         <v>60250014</v>
@@ -7695,7 +7368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A200" s="5">
         <f t="shared" si="6"/>
         <v>60250015</v>
@@ -7719,7 +7392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A201" s="5">
         <f t="shared" si="6"/>
         <v>60250016</v>
@@ -7743,7 +7416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A202" s="5">
         <f t="shared" si="6"/>
         <v>60250017</v>
@@ -7767,7 +7440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A203" s="5">
         <f t="shared" si="6"/>
         <v>60250018</v>
@@ -7791,7 +7464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A204" s="5">
         <f t="shared" si="6"/>
         <v>60250019</v>
@@ -7815,7 +7488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A205" s="5">
         <f t="shared" si="6"/>
         <v>60250020</v>
@@ -7839,7 +7512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A206" s="5">
         <f t="shared" si="6"/>
         <v>60250021</v>
@@ -7863,7 +7536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A207" s="5">
         <f t="shared" si="6"/>
         <v>60250022</v>
@@ -7887,7 +7560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A208" s="5">
         <f t="shared" si="6"/>
         <v>60250023</v>
@@ -7911,7 +7584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A209" s="5">
         <f t="shared" si="6"/>
         <v>60250024</v>
@@ -7935,7 +7608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A210" s="5">
         <f t="shared" si="6"/>
         <v>60250025</v>
@@ -7959,7 +7632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A211" s="5">
         <f t="shared" si="6"/>
         <v>60250026</v>
@@ -7983,7 +7656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A212" s="5">
         <f t="shared" si="6"/>
         <v>60250027</v>
@@ -8007,7 +7680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A213" s="5">
         <f t="shared" si="6"/>
         <v>60250028</v>
@@ -8031,7 +7704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A214" s="5">
         <f t="shared" si="6"/>
         <v>60250029</v>
@@ -8055,7 +7728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A215" s="5">
         <f t="shared" si="6"/>
         <v>60250030</v>
@@ -8079,7 +7752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A216" s="5">
         <f t="shared" si="6"/>
         <v>60250031</v>
@@ -8103,7 +7776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A217" s="5">
         <f t="shared" si="6"/>
         <v>60250032</v>
@@ -8127,7 +7800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A218" s="5">
         <f t="shared" ref="A218:A240" si="7">(B218+500000)*100+C218+G218*1000</f>
         <v>60250033</v>
@@ -8151,7 +7824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A219" s="5">
         <f t="shared" si="7"/>
         <v>60250034</v>
@@ -8175,7 +7848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A220" s="5">
         <f t="shared" si="7"/>
         <v>60250035</v>
@@ -8199,7 +7872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A221" s="5">
         <f t="shared" si="7"/>
         <v>60250036</v>
@@ -8223,7 +7896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A222" s="5">
         <f t="shared" si="7"/>
         <v>60250037</v>
@@ -8247,7 +7920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A223" s="5">
         <f t="shared" si="7"/>
         <v>60250038</v>
@@ -8271,7 +7944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A224" s="5">
         <f t="shared" si="7"/>
         <v>60250039</v>
@@ -8295,7 +7968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A225" s="5">
         <f t="shared" si="7"/>
         <v>60250040</v>
@@ -8319,7 +7992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A226" s="5">
         <f t="shared" si="7"/>
         <v>60250041</v>
@@ -8343,7 +8016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A227" s="5">
         <f t="shared" si="7"/>
         <v>60250042</v>
@@ -8367,7 +8040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A228" s="5">
         <f t="shared" si="7"/>
         <v>60250043</v>
@@ -8391,7 +8064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A229" s="5">
         <f t="shared" si="7"/>
         <v>60250044</v>
@@ -8415,7 +8088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A230" s="5">
         <f t="shared" si="7"/>
         <v>60250045</v>
@@ -8439,7 +8112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A231" s="5">
         <f t="shared" si="7"/>
         <v>60250046</v>
@@ -8463,7 +8136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A232" s="5">
         <f t="shared" si="7"/>
         <v>60250047</v>
@@ -8487,7 +8160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A233" s="5">
         <f t="shared" si="7"/>
         <v>60250048</v>
@@ -8511,7 +8184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A234" s="5">
         <f t="shared" si="7"/>
         <v>60250049</v>
@@ -8535,7 +8208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:7">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A235" s="5">
         <f t="shared" si="7"/>
         <v>60250050</v>
@@ -8559,7 +8232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:7">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A236" s="5">
         <f t="shared" si="7"/>
         <v>60340001</v>
@@ -8583,7 +8256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A237" s="5">
         <f t="shared" si="7"/>
         <v>60340002</v>
@@ -8607,7 +8280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A238" s="5">
         <f t="shared" si="7"/>
         <v>60340003</v>
@@ -8631,7 +8304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:7">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A239" s="5">
         <f t="shared" si="7"/>
         <v>60340004</v>
@@ -8655,7 +8328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A240" s="5">
         <f t="shared" si="7"/>
         <v>60340005</v>
@@ -8679,7 +8352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A241" s="5">
         <f t="shared" ref="A241:A250" si="8">(B241+500000)*100+C241+G241*1000</f>
         <v>60350001</v>
@@ -8703,7 +8376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A242" s="5">
         <f t="shared" si="8"/>
         <v>60350002</v>
@@ -8727,7 +8400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A243" s="5">
         <f t="shared" si="8"/>
         <v>60350003</v>
@@ -8751,7 +8424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A244" s="5">
         <f t="shared" si="8"/>
         <v>60350004</v>
@@ -8775,7 +8448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A245" s="5">
         <f t="shared" si="8"/>
         <v>60350005</v>
@@ -8799,7 +8472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A246" s="5">
         <f t="shared" si="8"/>
         <v>60350006</v>
@@ -8823,7 +8496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A247" s="5">
         <f t="shared" si="8"/>
         <v>60350007</v>
@@ -8847,7 +8520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A248" s="5">
         <f t="shared" si="8"/>
         <v>60350008</v>
@@ -8871,7 +8544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A249" s="5">
         <f t="shared" si="8"/>
         <v>60350009</v>
@@ -8895,7 +8568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A250" s="5">
         <f t="shared" si="8"/>
         <v>60350010</v>
@@ -8919,7 +8592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A251" s="5">
         <f t="shared" ref="A251:A270" si="9">(B251+500000)*100+C251+G251*1000</f>
         <v>60350101</v>
@@ -8943,7 +8616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A252" s="5">
         <f t="shared" si="9"/>
         <v>60350102</v>
@@ -8967,7 +8640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A253" s="5">
         <f t="shared" si="9"/>
         <v>60350103</v>
@@ -8991,7 +8664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A254" s="5">
         <f t="shared" si="9"/>
         <v>60350104</v>
@@ -9015,7 +8688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A255" s="5">
         <f t="shared" si="9"/>
         <v>60350105</v>
@@ -9039,7 +8712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A256" s="5">
         <f t="shared" si="9"/>
         <v>60350106</v>
@@ -9063,7 +8736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A257" s="5">
         <f t="shared" si="9"/>
         <v>60350107</v>
@@ -9087,7 +8760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A258" s="5">
         <f t="shared" si="9"/>
         <v>60350108</v>
@@ -9111,7 +8784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A259" s="5">
         <f t="shared" si="9"/>
         <v>60350109</v>
@@ -9135,7 +8808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A260" s="5">
         <f t="shared" si="9"/>
         <v>60350110</v>
@@ -9159,7 +8832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A261" s="5">
         <f t="shared" si="9"/>
         <v>60360001</v>
@@ -9183,7 +8856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A262" s="5">
         <f t="shared" si="9"/>
         <v>60360002</v>
@@ -9207,7 +8880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A263" s="5">
         <f t="shared" si="9"/>
         <v>60360003</v>
@@ -9231,7 +8904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A264" s="5">
         <f t="shared" si="9"/>
         <v>60360004</v>
@@ -9255,7 +8928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A265" s="5">
         <f t="shared" si="9"/>
         <v>60360005</v>
@@ -9279,7 +8952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A266" s="5">
         <f t="shared" si="9"/>
         <v>60340101</v>
@@ -9303,7 +8976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A267" s="5">
         <f t="shared" si="9"/>
         <v>60340102</v>
@@ -9327,7 +9000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A268" s="5">
         <f t="shared" si="9"/>
         <v>60340103</v>
@@ -9351,7 +9024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A269" s="5">
         <f t="shared" si="9"/>
         <v>60340104</v>
@@ -9375,7 +9048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A270" s="5">
         <f t="shared" si="9"/>
         <v>60340105</v>
@@ -9399,7 +9072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A271" s="5">
         <f t="shared" ref="A271:A285" si="10">(B271+500000)*100+C271+G271*1000</f>
         <v>60200001</v>
@@ -9423,7 +9096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A272" s="5">
         <f t="shared" si="10"/>
         <v>60200002</v>
@@ -9447,7 +9120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A273" s="5">
         <f t="shared" si="10"/>
         <v>60200003</v>
@@ -9471,7 +9144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A274" s="5">
         <f t="shared" si="10"/>
         <v>60200004</v>
@@ -9495,7 +9168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A275" s="5">
         <f t="shared" si="10"/>
         <v>60200005</v>
@@ -9519,7 +9192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A276" s="5">
         <f t="shared" si="10"/>
         <v>60200006</v>
@@ -9543,7 +9216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A277" s="5">
         <f t="shared" si="10"/>
         <v>60200007</v>
@@ -9567,7 +9240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A278" s="5">
         <f t="shared" si="10"/>
         <v>60200008</v>
@@ -9591,7 +9264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A279" s="5">
         <f t="shared" si="10"/>
         <v>60200009</v>
@@ -9615,7 +9288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A280" s="5">
         <f t="shared" si="10"/>
         <v>60200010</v>
@@ -9639,7 +9312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A281" s="5">
         <f t="shared" si="10"/>
         <v>60200011</v>
@@ -9663,7 +9336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A282" s="5">
         <f t="shared" si="10"/>
         <v>60200012</v>
@@ -9687,7 +9360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A283" s="5">
         <f t="shared" si="10"/>
         <v>60200013</v>
@@ -9711,7 +9384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A284" s="5">
         <f t="shared" si="10"/>
         <v>60200014</v>
@@ -9735,7 +9408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A285" s="5">
         <f t="shared" si="10"/>
         <v>60200015</v>
@@ -9759,7 +9432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A286" s="5">
         <f t="shared" ref="A286:A325" si="11">(B286+500000)*100+C286+G286*1000</f>
         <v>60380001</v>
@@ -9783,7 +9456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A287" s="5">
         <f t="shared" si="11"/>
         <v>60380002</v>
@@ -9807,7 +9480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A288" s="5">
         <f t="shared" si="11"/>
         <v>60380003</v>
@@ -9831,7 +9504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A289" s="5">
         <f t="shared" si="11"/>
         <v>60380004</v>
@@ -9855,7 +9528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A290" s="5">
         <f t="shared" si="11"/>
         <v>60380005</v>
@@ -9879,7 +9552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A291" s="5">
         <f t="shared" si="11"/>
         <v>60380006</v>
@@ -9903,7 +9576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A292" s="5">
         <f t="shared" si="11"/>
         <v>60380007</v>
@@ -9927,7 +9600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A293" s="5">
         <f t="shared" si="11"/>
         <v>60380008</v>
@@ -9951,7 +9624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A294" s="5">
         <f t="shared" si="11"/>
         <v>60380009</v>
@@ -9975,7 +9648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A295" s="5">
         <f t="shared" si="11"/>
         <v>60380010</v>
@@ -9999,7 +9672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A296" s="5">
         <f t="shared" si="11"/>
         <v>60380011</v>
@@ -10023,7 +9696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A297" s="5">
         <f t="shared" si="11"/>
         <v>60380012</v>
@@ -10047,7 +9720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A298" s="5">
         <f t="shared" si="11"/>
         <v>60380013</v>
@@ -10071,7 +9744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A299" s="5">
         <f t="shared" si="11"/>
         <v>60380014</v>
@@ -10095,7 +9768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A300" s="5">
         <f t="shared" si="11"/>
         <v>60380015</v>
@@ -10119,7 +9792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A301" s="5">
         <f t="shared" si="11"/>
         <v>60380016</v>
@@ -10143,7 +9816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:7">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A302" s="5">
         <f t="shared" si="11"/>
         <v>60380017</v>
@@ -10167,7 +9840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:7">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A303" s="5">
         <f t="shared" si="11"/>
         <v>60380018</v>
@@ -10191,7 +9864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:7">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A304" s="5">
         <f t="shared" si="11"/>
         <v>60380019</v>
@@ -10215,7 +9888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:7">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A305" s="5">
         <f t="shared" si="11"/>
         <v>60380020</v>
@@ -10239,7 +9912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:7">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A306" s="5">
         <f t="shared" si="11"/>
         <v>60380021</v>
@@ -10263,7 +9936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:7">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A307" s="5">
         <f t="shared" si="11"/>
         <v>60380022</v>
@@ -10287,7 +9960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:7">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A308" s="5">
         <f t="shared" si="11"/>
         <v>60380023</v>
@@ -10311,7 +9984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:7">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A309" s="5">
         <f t="shared" si="11"/>
         <v>60380024</v>
@@ -10335,7 +10008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A310" s="5">
         <f t="shared" si="11"/>
         <v>60380025</v>
@@ -10359,7 +10032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:7">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A311" s="5">
         <f t="shared" si="11"/>
         <v>60380026</v>
@@ -10383,7 +10056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:7">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A312" s="5">
         <f t="shared" si="11"/>
         <v>60380027</v>
@@ -10407,7 +10080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:7">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A313" s="5">
         <f t="shared" si="11"/>
         <v>60380028</v>
@@ -10431,7 +10104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:7">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A314" s="5">
         <f t="shared" si="11"/>
         <v>60380029</v>
@@ -10455,7 +10128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:7">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A315" s="5">
         <f t="shared" si="11"/>
         <v>60380030</v>
@@ -10479,7 +10152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:7">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A316" s="5">
         <f t="shared" si="11"/>
         <v>60380031</v>
@@ -10503,7 +10176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:7">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A317" s="5">
         <f t="shared" si="11"/>
         <v>60380032</v>
@@ -10527,7 +10200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A318" s="5">
         <f t="shared" si="11"/>
         <v>60380033</v>
@@ -10551,7 +10224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:7">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A319" s="5">
         <f t="shared" si="11"/>
         <v>60380034</v>
@@ -10575,7 +10248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A320" s="5">
         <f t="shared" si="11"/>
         <v>60380035</v>
@@ -10599,7 +10272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A321" s="5">
         <f t="shared" si="11"/>
         <v>60380036</v>
@@ -10623,7 +10296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A322" s="5">
         <f t="shared" si="11"/>
         <v>60380037</v>
@@ -10647,7 +10320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A323" s="5">
         <f t="shared" si="11"/>
         <v>60380038</v>
@@ -10671,7 +10344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A324" s="5">
         <f t="shared" si="11"/>
         <v>60380039</v>
@@ -10695,7 +10368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A325" s="5">
         <f t="shared" si="11"/>
         <v>60380040</v>
@@ -10719,7 +10392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A326" s="5">
         <f t="shared" ref="A326:A335" si="12">(B326+500000)*100+C326+G326*1000</f>
         <v>60370001</v>
@@ -10743,7 +10416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A327" s="5">
         <f t="shared" si="12"/>
         <v>60370002</v>
@@ -10767,7 +10440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A328" s="5">
         <f t="shared" si="12"/>
         <v>60370003</v>
@@ -10791,7 +10464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A329" s="5">
         <f t="shared" si="12"/>
         <v>60370004</v>
@@ -10815,7 +10488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A330" s="5">
         <f t="shared" si="12"/>
         <v>60370005</v>
@@ -10839,7 +10512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A331" s="5">
         <f t="shared" si="12"/>
         <v>60370006</v>
@@ -10863,7 +10536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A332" s="5">
         <f t="shared" si="12"/>
         <v>60370007</v>
@@ -10887,7 +10560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A333" s="5">
         <f t="shared" si="12"/>
         <v>60370008</v>
@@ -10911,7 +10584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A334" s="5">
         <f t="shared" si="12"/>
         <v>60370009</v>
@@ -10935,7 +10608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A335" s="5">
         <f t="shared" si="12"/>
         <v>60370010</v>
@@ -10959,7 +10632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:7">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A336" s="5">
         <f t="shared" ref="A336:A360" si="13">(B336+500000)*100+C336+G336*1000</f>
         <v>60310001</v>
@@ -10983,7 +10656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A337" s="5">
         <f t="shared" si="13"/>
         <v>60310002</v>
@@ -11007,7 +10680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A338" s="5">
         <f t="shared" si="13"/>
         <v>60310003</v>
@@ -11031,7 +10704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A339" s="5">
         <f t="shared" si="13"/>
         <v>60310004</v>
@@ -11055,7 +10728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:7">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A340" s="5">
         <f t="shared" si="13"/>
         <v>60310005</v>
@@ -11079,7 +10752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:7">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A341" s="5">
         <f t="shared" si="13"/>
         <v>60310006</v>
@@ -11103,7 +10776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A342" s="5">
         <f t="shared" si="13"/>
         <v>60310007</v>
@@ -11127,7 +10800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:7">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A343" s="5">
         <f t="shared" si="13"/>
         <v>60310008</v>
@@ -11151,7 +10824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:7">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A344" s="5">
         <f t="shared" si="13"/>
         <v>60310009</v>
@@ -11175,7 +10848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A345" s="5">
         <f t="shared" si="13"/>
         <v>60310010</v>
@@ -11199,7 +10872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:7">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A346" s="5">
         <f t="shared" si="13"/>
         <v>60310011</v>
@@ -11223,7 +10896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A347" s="5">
         <f t="shared" si="13"/>
         <v>60310012</v>
@@ -11247,7 +10920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A348" s="5">
         <f t="shared" si="13"/>
         <v>60310013</v>
@@ -11271,7 +10944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:7">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A349" s="5">
         <f t="shared" si="13"/>
         <v>60310014</v>
@@ -11295,7 +10968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:7">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A350" s="5">
         <f t="shared" si="13"/>
         <v>60310015</v>
@@ -11319,7 +10992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:7">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A351" s="5">
         <f t="shared" si="13"/>
         <v>60310016</v>
@@ -11343,7 +11016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:7">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A352" s="5">
         <f t="shared" si="13"/>
         <v>60310017</v>
@@ -11367,7 +11040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:7">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A353" s="5">
         <f t="shared" si="13"/>
         <v>60310018</v>
@@ -11391,7 +11064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:7">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A354" s="5">
         <f t="shared" si="13"/>
         <v>60310019</v>
@@ -11415,7 +11088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:7">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A355" s="5">
         <f t="shared" si="13"/>
         <v>60310020</v>
@@ -11439,7 +11112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:7">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A356" s="5">
         <f t="shared" si="13"/>
         <v>60310021</v>
@@ -11463,7 +11136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A357" s="5">
         <f t="shared" si="13"/>
         <v>60310022</v>
@@ -11487,7 +11160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A358" s="5">
         <f t="shared" si="13"/>
         <v>60310023</v>
@@ -11511,7 +11184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:7">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A359" s="5">
         <f t="shared" si="13"/>
         <v>60310024</v>
@@ -11535,7 +11208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:7">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A360" s="5">
         <f t="shared" si="13"/>
         <v>60310025</v>
@@ -11559,7 +11232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A361" s="5">
         <f t="shared" ref="A361:A400" si="14">(B361+500000)*100+C361+G361*1000</f>
         <v>60400001</v>
@@ -11583,7 +11256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A362" s="5">
         <f t="shared" si="14"/>
         <v>60400002</v>
@@ -11607,7 +11280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A363" s="5">
         <f t="shared" si="14"/>
         <v>60400003</v>
@@ -11631,7 +11304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:7">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A364" s="5">
         <f t="shared" si="14"/>
         <v>60400004</v>
@@ -11655,7 +11328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:7">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A365" s="5">
         <f t="shared" si="14"/>
         <v>60400005</v>
@@ -11679,7 +11352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:7">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A366" s="5">
         <f t="shared" si="14"/>
         <v>60400006</v>
@@ -11703,7 +11376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:7">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A367" s="5">
         <f t="shared" si="14"/>
         <v>60400007</v>
@@ -11727,7 +11400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:7">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A368" s="5">
         <f t="shared" si="14"/>
         <v>60400008</v>
@@ -11751,7 +11424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A369" s="5">
         <f t="shared" si="14"/>
         <v>60400009</v>
@@ -11775,7 +11448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:7">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A370" s="5">
         <f t="shared" si="14"/>
         <v>60400010</v>
@@ -11799,7 +11472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A371" s="5">
         <f t="shared" si="14"/>
         <v>60400011</v>
@@ -11823,7 +11496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A372" s="5">
         <f t="shared" si="14"/>
         <v>60400012</v>
@@ -11847,7 +11520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A373" s="5">
         <f t="shared" si="14"/>
         <v>60400013</v>
@@ -11871,7 +11544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A374" s="5">
         <f t="shared" si="14"/>
         <v>60400014</v>
@@ -11895,7 +11568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A375" s="5">
         <f t="shared" si="14"/>
         <v>60400015</v>
@@ -11919,7 +11592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A376" s="5">
         <f t="shared" si="14"/>
         <v>60400016</v>
@@ -11943,7 +11616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A377" s="5">
         <f t="shared" si="14"/>
         <v>60400017</v>
@@ -11967,7 +11640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A378" s="5">
         <f t="shared" si="14"/>
         <v>60400018</v>
@@ -11991,7 +11664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A379" s="5">
         <f t="shared" si="14"/>
         <v>60400019</v>
@@ -12015,7 +11688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:7">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A380" s="5">
         <f t="shared" si="14"/>
         <v>60400020</v>
@@ -12039,7 +11712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A381" s="5">
         <f t="shared" si="14"/>
         <v>60400021</v>
@@ -12063,7 +11736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:7">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A382" s="5">
         <f t="shared" si="14"/>
         <v>60400022</v>
@@ -12087,7 +11760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:7">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A383" s="5">
         <f t="shared" si="14"/>
         <v>60400023</v>
@@ -12111,7 +11784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A384" s="5">
         <f t="shared" si="14"/>
         <v>60400024</v>
@@ -12135,7 +11808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A385" s="5">
         <f t="shared" si="14"/>
         <v>60400025</v>
@@ -12159,7 +11832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A386" s="5">
         <f t="shared" si="14"/>
         <v>60400026</v>
@@ -12183,7 +11856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A387" s="5">
         <f t="shared" si="14"/>
         <v>60400027</v>
@@ -12207,7 +11880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A388" s="5">
         <f t="shared" si="14"/>
         <v>60400028</v>
@@ -12231,7 +11904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:7">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A389" s="5">
         <f t="shared" si="14"/>
         <v>60400029</v>
@@ -12255,7 +11928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:7">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A390" s="5">
         <f t="shared" si="14"/>
         <v>60400030</v>
@@ -12279,7 +11952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A391" s="5">
         <f t="shared" si="14"/>
         <v>60400031</v>
@@ -12303,7 +11976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A392" s="5">
         <f t="shared" si="14"/>
         <v>60400032</v>
@@ -12327,7 +12000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A393" s="5">
         <f t="shared" si="14"/>
         <v>60400033</v>
@@ -12351,7 +12024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A394" s="5">
         <f t="shared" si="14"/>
         <v>60400034</v>
@@ -12375,7 +12048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A395" s="5">
         <f t="shared" si="14"/>
         <v>60400035</v>
@@ -12399,7 +12072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:7">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A396" s="5">
         <f t="shared" si="14"/>
         <v>60400036</v>
@@ -12423,7 +12096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:7">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A397" s="5">
         <f t="shared" si="14"/>
         <v>60400037</v>
@@ -12447,7 +12120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:7">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A398" s="5">
         <f t="shared" si="14"/>
         <v>60400038</v>
@@ -12471,7 +12144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:7">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A399" s="5">
         <f t="shared" si="14"/>
         <v>60400039</v>
@@ -12495,7 +12168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:7">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A400" s="5">
         <f t="shared" si="14"/>
         <v>60400040</v>
@@ -12519,7 +12192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:7">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A401" s="5">
         <f t="shared" ref="A401:A425" si="15">(B401+500000)*100+C401+G401*1000</f>
         <v>60390001</v>
@@ -12543,7 +12216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:7">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A402" s="5">
         <f t="shared" si="15"/>
         <v>60390002</v>
@@ -12567,7 +12240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:7">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A403" s="5">
         <f t="shared" si="15"/>
         <v>60390003</v>
@@ -12591,7 +12264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:7">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A404" s="5">
         <f t="shared" si="15"/>
         <v>60390004</v>
@@ -12615,7 +12288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:7">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A405" s="5">
         <f t="shared" si="15"/>
         <v>60390005</v>
@@ -12639,7 +12312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:7">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A406" s="5">
         <f t="shared" si="15"/>
         <v>60390006</v>
@@ -12663,7 +12336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:7">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A407" s="5">
         <f t="shared" si="15"/>
         <v>60390007</v>
@@ -12687,7 +12360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:7">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A408" s="5">
         <f t="shared" si="15"/>
         <v>60390008</v>
@@ -12711,7 +12384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:7">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A409" s="5">
         <f t="shared" si="15"/>
         <v>60390009</v>
@@ -12735,7 +12408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:7">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A410" s="5">
         <f t="shared" si="15"/>
         <v>60390010</v>
@@ -12759,7 +12432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:7">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A411" s="5">
         <f t="shared" si="15"/>
         <v>60390011</v>
@@ -12783,7 +12456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:7">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A412" s="5">
         <f t="shared" si="15"/>
         <v>60390012</v>
@@ -12807,7 +12480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:7">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A413" s="5">
         <f t="shared" si="15"/>
         <v>60390013</v>
@@ -12831,7 +12504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:7">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A414" s="5">
         <f t="shared" si="15"/>
         <v>60390014</v>
@@ -12855,7 +12528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:7">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A415" s="5">
         <f t="shared" si="15"/>
         <v>60390015</v>
@@ -12879,7 +12552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:7">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A416" s="5">
         <f t="shared" si="15"/>
         <v>60390016</v>
@@ -12903,7 +12576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:7">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A417" s="5">
         <f t="shared" si="15"/>
         <v>60390017</v>
@@ -12927,7 +12600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:7">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A418" s="5">
         <f t="shared" si="15"/>
         <v>60390018</v>
@@ -12951,7 +12624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:7">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A419" s="5">
         <f t="shared" si="15"/>
         <v>60390019</v>
@@ -12975,7 +12648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:7">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A420" s="5">
         <f t="shared" si="15"/>
         <v>60390020</v>
@@ -12999,7 +12672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:7">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A421" s="5">
         <f t="shared" si="15"/>
         <v>60390021</v>
@@ -13023,7 +12696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:7">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A422" s="5">
         <f t="shared" si="15"/>
         <v>60390022</v>
@@ -13047,7 +12720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:7">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A423" s="5">
         <f t="shared" si="15"/>
         <v>60390023</v>
@@ -13071,7 +12744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:7">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A424" s="5">
         <f t="shared" si="15"/>
         <v>60390024</v>
@@ -13095,7 +12768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:7">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A425" s="5">
         <f t="shared" si="15"/>
         <v>60390025</v>
@@ -13119,7 +12792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" customFormat="1" spans="1:7">
+    <row r="426" spans="1:7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A426" s="16">
         <v>60550001</v>
       </c>
@@ -13142,7 +12815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" customFormat="1" spans="1:7">
+    <row r="427" spans="1:7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A427" s="16">
         <v>60550002</v>
       </c>
@@ -13165,7 +12838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" customFormat="1" spans="1:7">
+    <row r="428" spans="1:7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A428" s="16">
         <v>60550003</v>
       </c>
@@ -13188,7 +12861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" customFormat="1" spans="1:7">
+    <row r="429" spans="1:7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A429" s="16">
         <v>60550004</v>
       </c>
@@ -13211,7 +12884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" customFormat="1" spans="1:7">
+    <row r="430" spans="1:7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A430" s="16">
         <v>60550005</v>
       </c>
@@ -13234,7 +12907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" customFormat="1" spans="1:7">
+    <row r="431" spans="1:7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A431" s="16">
         <v>60550101</v>
       </c>
@@ -13257,7 +12930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" customFormat="1" spans="1:7">
+    <row r="432" spans="1:7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A432" s="16">
         <v>60550102</v>
       </c>
@@ -13280,7 +12953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" customFormat="1" spans="1:7">
+    <row r="433" spans="1:7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A433" s="16">
         <v>60550103</v>
       </c>
@@ -13303,7 +12976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" customFormat="1" spans="1:7">
+    <row r="434" spans="1:7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A434" s="16">
         <v>60550104</v>
       </c>
@@ -13326,7 +12999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" customFormat="1" spans="1:7">
+    <row r="435" spans="1:7" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A435" s="16">
         <v>60550105</v>
       </c>
@@ -13349,94 +13022,208 @@
         <v>0</v>
       </c>
     </row>
+    <row r="436" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A436" s="17">
+        <v>60550201</v>
+      </c>
+      <c r="B436" s="18">
+        <v>105502</v>
+      </c>
+      <c r="C436" s="19">
+        <v>1</v>
+      </c>
+      <c r="D436" s="17">
+        <v>1</v>
+      </c>
+      <c r="E436" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F436" s="19">
+        <v>5</v>
+      </c>
+      <c r="G436" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A437" s="17">
+        <v>60550202</v>
+      </c>
+      <c r="B437" s="18">
+        <v>105502</v>
+      </c>
+      <c r="C437" s="19">
+        <v>2</v>
+      </c>
+      <c r="D437" s="17">
+        <v>1</v>
+      </c>
+      <c r="E437" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F437" s="19">
+        <v>5</v>
+      </c>
+      <c r="G437" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A438" s="17">
+        <v>60550203</v>
+      </c>
+      <c r="B438" s="18">
+        <v>105502</v>
+      </c>
+      <c r="C438" s="19">
+        <v>3</v>
+      </c>
+      <c r="D438" s="17">
+        <v>1</v>
+      </c>
+      <c r="E438" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F438" s="19">
+        <v>5</v>
+      </c>
+      <c r="G438" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A439" s="17">
+        <v>60550204</v>
+      </c>
+      <c r="B439" s="18">
+        <v>105502</v>
+      </c>
+      <c r="C439" s="19">
+        <v>4</v>
+      </c>
+      <c r="D439" s="17">
+        <v>1</v>
+      </c>
+      <c r="E439" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="F439" s="19">
+        <v>5</v>
+      </c>
+      <c r="G439" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A440" s="17">
+        <v>60550205</v>
+      </c>
+      <c r="B440" s="18">
+        <v>105502</v>
+      </c>
+      <c r="C440" s="19">
+        <v>5</v>
+      </c>
+      <c r="D440" s="17">
+        <v>1</v>
+      </c>
+      <c r="E440" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="F440" s="19">
+        <v>5</v>
+      </c>
+      <c r="G440" s="17">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="E161:E185">
+    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E186:E235">
+    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E236">
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E237">
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E238">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E239">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E240">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E241:E250">
+    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E251:E260">
+    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E261">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E262">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E263">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E264">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E265">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E266">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E267">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E268">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E269">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E270">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E161:E185">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E186:E235">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E241:E250">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E251:E260">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E271:E285">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E286:E325">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E326:E335">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E361:E400">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E401:E403">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="E20:S28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="20" ht="33" spans="5:19">
+    <row r="20" spans="5:19" ht="33" x14ac:dyDescent="0.15">
       <c r="E20" s="1" t="s">
         <v>0</v>
       </c>
@@ -13479,7 +13266,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="5:19">
+    <row r="21" spans="5:19" ht="16.5" x14ac:dyDescent="0.15">
       <c r="E21" s="5" t="s">
         <v>7</v>
       </c>
@@ -13520,7 +13307,7 @@
       </c>
       <c r="S21" s="7"/>
     </row>
-    <row r="22" ht="16.5" spans="5:19">
+    <row r="22" spans="5:19" ht="16.5" x14ac:dyDescent="0.15">
       <c r="E22" s="5" t="s">
         <v>0</v>
       </c>
@@ -13559,7 +13346,7 @@
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
     </row>
-    <row r="23" ht="16.5" spans="5:19">
+    <row r="23" spans="5:19" ht="16.5" x14ac:dyDescent="0.15">
       <c r="E23" s="5"/>
       <c r="F23" s="6"/>
       <c r="G23" s="7"/>
@@ -13576,7 +13363,7 @@
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
     </row>
-    <row r="24" ht="16.5" spans="5:19">
+    <row r="24" spans="5:19" ht="16.5" x14ac:dyDescent="0.15">
       <c r="E24" s="5">
         <v>1</v>
       </c>
@@ -13615,7 +13402,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="25" ht="16.5" spans="5:19">
+    <row r="25" spans="5:19" ht="16.5" x14ac:dyDescent="0.15">
       <c r="E25" s="5">
         <v>2</v>
       </c>
@@ -13654,7 +13441,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="26" ht="16.5" spans="5:19">
+    <row r="26" spans="5:19" ht="16.5" x14ac:dyDescent="0.15">
       <c r="E26" s="5">
         <v>3</v>
       </c>
@@ -13677,7 +13464,7 @@
       <c r="R26" s="7"/>
       <c r="S26" s="7"/>
     </row>
-    <row r="27" ht="16.5" spans="5:19">
+    <row r="27" spans="5:19" ht="16.5" x14ac:dyDescent="0.15">
       <c r="E27" s="5">
         <v>4</v>
       </c>
@@ -13700,7 +13487,7 @@
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
     </row>
-    <row r="28" ht="16.5" spans="5:19">
+    <row r="28" spans="5:19" ht="16.5" x14ac:dyDescent="0.15">
       <c r="E28" s="5">
         <v>5</v>
       </c>
@@ -13740,8 +13527,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>